--- a/data/trans_dic/P22$concerEmp-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerEmp-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado por su empresa</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado por su empresa (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,44</t>
+          <t>0,94; 3,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,64</t>
+          <t>0,47; 2,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,36</t>
+          <t>0,58; 3,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,35</t>
+          <t>0,85; 3,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,15</t>
+          <t>0,33; 3,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,78</t>
+          <t>0,6; 3,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,47</t>
+          <t>0,25; 2,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,59</t>
+          <t>0,54; 2,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,79</t>
+          <t>0,92; 2,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,54</t>
+          <t>0,79; 2,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,46</t>
+          <t>0,59; 2,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,57</t>
+          <t>0,95; 2,56</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,45</t>
+          <t>1,01; 4,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,87</t>
+          <t>1,74; 6,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,36</t>
+          <t>0,53; 3,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,19</t>
+          <t>1,63; 5,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,04</t>
+          <t>0,91; 3,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,77</t>
+          <t>0,62; 2,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,5</t>
+          <t>1,32; 3,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,77</t>
+          <t>1,2; 3,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,09</t>
+          <t>0,39; 1,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,52</t>
+          <t>1,36; 3,58</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,3</t>
+          <t>1,52; 4,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,91</t>
+          <t>0,33; 2,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,7</t>
+          <t>0,25; 2,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,23</t>
+          <t>1,22; 3,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,34</t>
+          <t>0,23; 1,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,23</t>
+          <t>0,34; 2,16</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,34</t>
+          <t>1,55; 3,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,92</t>
+          <t>0,6; 1,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,91</t>
+          <t>0,09; 1,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,01</t>
+          <t>0,35; 2,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,31</t>
+          <t>0,13; 1,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,32 +1167,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,49</t>
+          <t>0,26; 1,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,03</t>
+          <t>0,19; 1,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,42</t>
+          <t>1,12; 2,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,37</t>
+          <t>0,47; 1,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,88</t>
+          <t>0,23; 0,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,25</t>
+          <t>0,35; 1,34</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,4</t>
+          <t>2,0; 6,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,54</t>
+          <t>0,67; 3,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,74</t>
+          <t>0,06; 0,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,69</t>
+          <t>0,96; 2,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,49</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,33</t>
+          <t>0,0; 0,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,46</t>
+          <t>0,38; 1,55</t>
         </is>
       </c>
     </row>
@@ -1417,42 +1417,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,41</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,51</t>
+          <t>0,11; 1,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,06</t>
+          <t>0,09; 1,06</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,77</t>
+          <t>1,76; 2,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,6</t>
+          <t>0,81; 1,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,9</t>
+          <t>0,33; 0,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,92</t>
+          <t>0,97; 1,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,82</t>
+          <t>0,32; 0,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,6</t>
+          <t>0,2; 0,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,61</t>
+          <t>0,2; 0,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,95</t>
+          <t>0,42; 0,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,68</t>
+          <t>1,1; 1,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,98</t>
+          <t>0,56; 1,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,68</t>
+          <t>0,32; 0,69</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,33</t>
+          <t>0,78; 1,31</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado por su empresa</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado por su empresa (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3963; 16242</t>
+          <t>4431; 16007</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2013; 11528</t>
+          <t>2057; 12132</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2055; 14432</t>
+          <t>2475; 15978</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4225; 16901</t>
+          <t>4315; 17153</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1020; 9676</t>
+          <t>1014; 9567</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1870; 11895</t>
+          <t>1892; 11341</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>876; 8578</t>
+          <t>876; 7772</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2806; 11608</t>
+          <t>2398; 11338</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6904; 21710</t>
+          <t>7143; 21612</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5172; 19074</t>
+          <t>5928; 19037</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4510; 19080</t>
+          <t>4572; 18890</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8678; 24492</t>
+          <t>9041; 24346</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3672; 16320</t>
+          <t>3708; 16096</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7536; 24600</t>
+          <t>7297; 25467</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1934; 12661</t>
+          <t>1986; 13889</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7122; 23448</t>
+          <t>7367; 23919</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3560; 15032</t>
+          <t>3375; 14177</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6303</t>
+          <t>0; 6957</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6104</t>
+          <t>0; 6339</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2069; 10591</t>
+          <t>2380; 10791</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9230; 25843</t>
+          <t>9750; 27109</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9653; 28519</t>
+          <t>9077; 27115</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3413; 15608</t>
+          <t>2948; 14415</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11271; 29354</t>
+          <t>11383; 29893</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8393; 23263</t>
+          <t>8254; 22249</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2797; 12027</t>
+          <t>2078; 12877</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 8292</t>
+          <t>0; 10652</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1661; 18015</t>
+          <t>1651; 18815</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1951</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2038</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5103</t>
+          <t>0; 5579</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4188</t>
+          <t>0; 4594</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8324; 22894</t>
+          <t>8634; 22826</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2084; 11951</t>
+          <t>2064; 12225</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 9906</t>
+          <t>0; 10557</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2738; 18589</t>
+          <t>2827; 18026</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17998; 41270</t>
+          <t>19105; 41939</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6788; 22208</t>
+          <t>6978; 22432</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>982; 10456</t>
+          <t>984; 11434</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3596; 20749</t>
+          <t>3585; 22144</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>943; 9358</t>
+          <t>941; 8678</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>946; 7976</t>
+          <t>952; 7936</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2050; 12275</t>
+          <t>2117; 12871</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1577; 10069</t>
+          <t>1838; 10387</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22340; 47095</t>
+          <t>21858; 45534</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9639; 26299</t>
+          <t>9059; 25197</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4325; 17282</t>
+          <t>4527; 17944</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7259; 25140</t>
+          <t>7104; 26932</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6568; 22434</t>
+          <t>7004; 21299</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4490</t>
+          <t>0; 4453</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1993</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2603; 16809</t>
+          <t>3200; 16335</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8035</t>
+          <t>0; 7946</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4614</t>
+          <t>0; 5365</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5224</t>
+          <t>0; 5027</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>687; 6224</t>
+          <t>485; 5727</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8102; 24745</t>
+          <t>8848; 25107</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6216</t>
+          <t>0; 6518</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4440</t>
+          <t>0; 4871</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4616; 19193</t>
+          <t>4998; 20308</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4892</t>
+          <t>0; 4923</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5671</t>
+          <t>0; 6759</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4080</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5101</t>
+          <t>0; 5838</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 7054</t>
+          <t>0; 7258</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2092</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>881; 11464</t>
+          <t>843; 9779</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6942</t>
+          <t>0; 6938</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 7115</t>
+          <t>0; 6145</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 7009</t>
+          <t>0; 6989</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>814; 10581</t>
+          <t>874; 10654</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>57455; 90484</t>
+          <t>57327; 91508</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28157; 54666</t>
+          <t>27706; 55629</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10866; 30587</t>
+          <t>11276; 30706</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32187; 64730</t>
+          <t>32650; 64786</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11161; 27842</t>
+          <t>10786; 28293</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6927; 21178</t>
+          <t>7218; 22838</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6972; 21612</t>
+          <t>6989; 19992</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15862; 33788</t>
+          <t>15191; 33840</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>73436; 111681</t>
+          <t>72951; 111573</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39671; 68517</t>
+          <t>39243; 69828</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21848; 46798</t>
+          <t>22058; 47384</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>53629; 92574</t>
+          <t>54389; 91154</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$concerEmp-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerEmp-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,39</t>
+          <t>0,95; 3,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,77</t>
+          <t>0,46; 2,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,72</t>
+          <t>0,49; 3,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,4</t>
+          <t>0,78; 2,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,12</t>
+          <t>0,33; 3,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,61</t>
+          <t>0,62; 3,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,24</t>
+          <t>0,25; 2,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,53</t>
+          <t>0,58; 2,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,77</t>
+          <t>0,96; 2,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,53</t>
+          <t>0,69; 2,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,43</t>
+          <t>0,57; 2,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,56</t>
+          <t>0,9; 2,46</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,39</t>
+          <t>1,11; 4,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,08</t>
+          <t>1,8; 6,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,69</t>
+          <t>0,5; 3,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,29</t>
+          <t>1,69; 5,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,81</t>
+          <t>0,87; 3,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,82</t>
+          <t>0,52; 2,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,67</t>
+          <t>1,18; 3,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,58</t>
+          <t>1,11; 3,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,93</t>
+          <t>0,39; 2,01</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,58</t>
+          <t>1,33; 3,49</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,11</t>
+          <t>1,5; 4,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,05</t>
+          <t>0,32; 1,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,82</t>
+          <t>0,75; 3,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1027,32 +1027,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,22</t>
+          <t>1,09; 3,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,37</t>
+          <t>0,23; 1,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,16</t>
+          <t>0,71; 2,8</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,4</t>
+          <t>1,57; 3,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,94</t>
+          <t>0,61; 1,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,0</t>
+          <t>0,08; 0,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,14</t>
+          <t>0,36; 1,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,21</t>
+          <t>0,13; 1,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,04</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,57</t>
+          <t>0,34; 1,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,06</t>
+          <t>0,25; 1,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,34</t>
+          <t>1,16; 2,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,31</t>
+          <t>0,47; 1,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,91</t>
+          <t>0,25; 0,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,34</t>
+          <t>0,48; 1,48</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,08</t>
+          <t>1,94; 6,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,54 +1292,54 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,44</t>
+          <t>0,53; 2,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,68</t>
+          <t>0,09; 0,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,73</t>
+          <t>0,86; 2,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,36</t>
+          <t>0,0; 0,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,55</t>
+          <t>0,36; 1,43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,47</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,28</t>
+          <t>0,1; 1,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,45</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,45</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,06</t>
+          <t>0,06; 0,9</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,8</t>
+          <t>1,8; 2,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,63</t>
+          <t>0,79; 1,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,91</t>
+          <t>0,33; 0,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,92</t>
+          <t>1,1; 2,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,84</t>
+          <t>0,32; 0,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,64</t>
+          <t>0,2; 0,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,57</t>
+          <t>0,2; 0,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,95</t>
+          <t>0,47; 1,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,68</t>
+          <t>1,1; 1,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,0</t>
+          <t>0,58; 0,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,69</t>
+          <t>0,3; 0,65</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,31</t>
+          <t>0,84; 1,36</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>15978</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4431; 16007</t>
+          <t>4491; 15680</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2057; 12132</t>
+          <t>2007; 11512</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2475; 15978</t>
+          <t>2116; 14797</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4315; 17153</t>
+          <t>4274; 16407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1014; 9567</t>
+          <t>1020; 10468</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1892; 11341</t>
+          <t>1952; 12270</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>876; 7772</t>
+          <t>875; 7704</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2398; 11338</t>
+          <t>2834; 11553</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7143; 21612</t>
+          <t>7443; 21197</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5928; 19037</t>
+          <t>5170; 18667</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4572; 18890</t>
+          <t>4435; 19940</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9041; 24346</t>
+          <t>9397; 25535</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>14868</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>20416</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3708; 16096</t>
+          <t>4067; 15636</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7297; 25467</t>
+          <t>7526; 25904</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1986; 13889</t>
+          <t>1892; 12380</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7367; 23919</t>
+          <t>8143; 26100</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3375; 14177</t>
+          <t>3238; 14576</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6957</t>
+          <t>0; 7004</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6339</t>
+          <t>0; 7346</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2380; 10791</t>
+          <t>2190; 10678</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9750; 27109</t>
+          <t>8749; 25306</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9077; 27115</t>
+          <t>8424; 27833</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2948; 14415</t>
+          <t>2909; 15052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11383; 29893</t>
+          <t>12017; 31636</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>9625</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8254; 22249</t>
+          <t>8108; 22521</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2078; 12877</t>
+          <t>2018; 11802</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 10652</t>
+          <t>0; 8255</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1651; 18815</t>
+          <t>3532; 15810</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2373,32 +2373,32 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5579</t>
+          <t>0; 5824</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4594</t>
+          <t>0; 4830</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8634; 22826</t>
+          <t>7719; 22685</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2064; 12225</t>
+          <t>2040; 12737</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 10557</t>
+          <t>0; 8815</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2827; 18026</t>
+          <t>4703; 18474</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>16788</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19105; 41939</t>
+          <t>19357; 41781</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6978; 22432</t>
+          <t>7072; 22279</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>984; 11434</t>
+          <t>973; 10832</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3585; 22144</t>
+          <t>4097; 22187</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>941; 8678</t>
+          <t>947; 9074</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>952; 7936</t>
+          <t>0; 7923</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2117; 12871</t>
+          <t>2820; 12565</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1838; 10387</t>
+          <t>2177; 10072</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21858; 45534</t>
+          <t>22578; 46828</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9059; 25197</t>
+          <t>9116; 26101</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4527; 17944</t>
+          <t>4888; 17930</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7104; 26932</t>
+          <t>9549; 29531</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>10346</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2759,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7004; 21299</t>
+          <t>6814; 22314</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4453</t>
+          <t>0; 4944</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2774,54 +2774,54 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3200; 16335</t>
+          <t>3011; 15885</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7946</t>
+          <t>0; 7070</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5365</t>
+          <t>0; 5861</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5027</t>
+          <t>0; 4438</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>485; 5727</t>
+          <t>709; 7087</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8848; 25107</t>
+          <t>7929; 23716</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6518</t>
+          <t>0; 5804</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4871</t>
+          <t>0; 4420</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4998; 20308</t>
+          <t>5081; 19945</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3228</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4923</t>
+          <t>0; 4905</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6759</t>
+          <t>0; 6985</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5838</t>
+          <t>0; 6742</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 7258</t>
+          <t>0; 6450</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>843; 9779</t>
+          <t>862; 10364</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6938</t>
+          <t>0; 6064</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 6145</t>
+          <t>0; 7077</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 6989</t>
+          <t>0; 7005</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>874; 10654</t>
+          <t>671; 9774</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47780</t>
+          <t>51625</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>23200</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>70980</t>
+          <t>76381</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>57327; 91508</t>
+          <t>58757; 91488</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27706; 55629</t>
+          <t>27177; 54281</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11276; 30706</t>
+          <t>11108; 32112</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32650; 64786</t>
+          <t>37731; 70111</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10786; 28293</t>
+          <t>10660; 27896</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7218; 22838</t>
+          <t>7077; 21651</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6989; 19992</t>
+          <t>7014; 20761</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15191; 33840</t>
+          <t>17251; 36416</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>72951; 111573</t>
+          <t>73290; 111954</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39243; 69828</t>
+          <t>40195; 68552</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22058; 47384</t>
+          <t>20939; 44862</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>54389; 91154</t>
+          <t>59148; 96513</t>
         </is>
       </c>
     </row>
